--- a/fixtures/ficticios/siddex/pedidos.xlsx
+++ b/fixtures/ficticios/siddex/pedidos.xlsx
@@ -482,7 +482,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20261060</v>
+        <v>20269060</v>
       </c>
       <c r="B4" t="n">
         <v>9001</v>
@@ -494,7 +494,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>134.000.842</t>
+          <t>900.000.842</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -521,13 +521,13 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PVCC550942</t>
+          <t>FXT9550942</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20261060</v>
+        <v>20269060</v>
       </c>
       <c r="B5" t="n">
         <v>9001</v>
@@ -539,7 +539,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>I33.000.786</t>
+          <t>Z33.000.786</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -572,7 +572,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20261060</v>
+        <v>20269060</v>
       </c>
       <c r="B6" t="n">
         <v>9001</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20261061</v>
+        <v>20269061</v>
       </c>
       <c r="B7" t="n">
         <v>9003</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20261061</v>
+        <v>20269061</v>
       </c>
       <c r="B8" t="n">
         <v>9003</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20261055</v>
+        <v>20269055</v>
       </c>
       <c r="B9" t="n">
         <v>9002</v>
